--- a/skills/mfg-improvement-frameworks/assets/qc-process-table.xlsx
+++ b/skills/mfg-improvement-frameworks/assets/qc-process-table.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,13 +570,15 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>【記入方法】黄色のセルに記入する。9行目は記入例（削除して使う）。管理特性＝工程で制御する条件、品質特性＝結果として得られる値。</t>
-        </is>
-      </c>
-    </row>
+          <t>【記入方法】黄色のセルに記入する。9行目は記入例（削除して使う）。管理特性＝工程で制御する条件、品質特性＝結果として得られる値。「外れると起きること」は、なぜその項目を管理するかが表だけで読めるように、外れたときに起きる不良・損失を書く（未確認なら「未確認」と書く）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -640,6 +643,12 @@
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>外れると起きること
+(管理する理由)</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>異常時の処置</t>
         </is>
@@ -705,6 +714,11 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>板厚が薄いと曲げ工程で割れる</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>受入不合格処理へ</t>
         </is>
@@ -724,6 +738,7 @@
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -739,6 +754,7 @@
       <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -754,6 +770,7 @@
       <c r="K14" s="7" t="n"/>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -769,6 +786,7 @@
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -784,6 +802,7 @@
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -799,6 +818,7 @@
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -814,6 +834,7 @@
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -829,6 +850,7 @@
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -844,6 +866,7 @@
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -859,6 +882,7 @@
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -874,6 +898,7 @@
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
+      <c r="N22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -889,6 +914,7 @@
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -904,6 +930,7 @@
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
+      <c r="N24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -919,6 +946,7 @@
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -934,6 +962,7 @@
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -949,6 +978,7 @@
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -964,6 +994,7 @@
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -979,6 +1010,7 @@
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
+      <c r="N29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -994,6 +1026,7 @@
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
+      <c r="N30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1009,6 +1042,7 @@
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1024,6 +1058,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1039,6 +1074,7 @@
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1054,6 +1090,7 @@
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1069,6 +1106,7 @@
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1084,6 +1122,7 @@
       <c r="K36" s="7" t="n"/>
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/skills/mfg-improvement-frameworks/assets/qc-process-table.xlsx
+++ b/skills/mfg-improvement-frameworks/assets/qc-process-table.xlsx
@@ -570,15 +570,13 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>【記入方法】黄色のセルに記入する。9行目は記入例（削除して使う）。管理特性＝工程で制御する条件、品質特性＝結果として得られる値。「外れると起きること」は、なぜその項目を管理するかが表だけで読めるように、外れたときに起きる不良・損失を書く（未確認なら「未確認」と書く）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>【記入方法】黄色のセルに記入する。11行目は記入例（削除して使う。見出しは10行目）。管理特性＝工程で制御する条件、品質特性＝結果として得られる値。「外れると起きること」は、なぜその項目を管理するかが表だけで読めるように、外れたときに起きる不良・損失を書く（未確認なら「未確認」と書く）。 管理項目は部品名・機種名ではなく、新しい品種が入っても判定できる量で書く（×大型コネクタの予熱温度／○はんだ付け部の面積50mm²以上の予熱温度）。</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
